--- a/astro-site/public/dl/bar-checklist-templates/06-bar-event-checklists.xlsx
+++ b/astro-site/public/dl/bar-checklist-templates/06-bar-event-checklists.xlsx
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Define the concept for the night (party, dinner + open bar, ticket price)</t>
+          <t>Define the concept for the night (party or dinner, ticket price and what it includes); open bars and all-you-can-drink packages are banned in some states (e.g. Massachusetts): check your state's ABC/liquor authority</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Midnight toast for guests 21+ only (check ID), with a non-alcoholic option</t>
+          <t>Midnight toast for guests 21+ only (check ID), with a non-alcoholic option; build it into the ticket price where your state bans free drinks</t>
         </is>
       </c>
       <c r="C16" s="36" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Settle in writing the price per person and what it includes: number of pours, food pairing, farewell drink and whether there is a bottle to take home</t>
+          <t>Settle in writing the price per person and what it includes: number of pours, food pairing, farewell drink and any bottle to take home (check your license: not every on-premise license allows sealed bottles to go)</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
